--- a/docs/incentive.xlsx
+++ b/docs/incentive.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Gagan\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\kbelectricals\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6C3EFD-3118-45BB-A5FE-9551357E0E76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB71172-74BB-4B54-9014-CDACD3439582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sales KRA" sheetId="1" r:id="rId1"/>
@@ -146,9 +146,6 @@
     <t>C Class</t>
   </si>
   <si>
-    <t>Max 4 points</t>
-  </si>
-  <si>
     <t>Best Score</t>
   </si>
   <si>
@@ -432,6 +429,9 @@
   </si>
   <si>
     <t>&gt;1.5 Lakh</t>
+  </si>
+  <si>
+    <t>Max 5 points</t>
   </si>
 </sst>
 </file>
@@ -1049,24 +1049,60 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1076,25 +1112,10 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1106,40 +1127,19 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1445,22 +1445,22 @@
     <row r="1" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:15" ht="33" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="22"/>
-      <c r="B2" s="76" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="77"/>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77"/>
-      <c r="G2" s="77"/>
-      <c r="H2" s="77"/>
-      <c r="I2" s="77"/>
-      <c r="J2" s="77"/>
-      <c r="K2" s="77"/>
-      <c r="L2" s="77"/>
-      <c r="M2" s="77"/>
-      <c r="N2" s="77"/>
-      <c r="O2" s="78"/>
+      <c r="B2" s="54" t="s">
+        <v>54</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="56"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="23"/>
@@ -1468,44 +1468,44 @@
     <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H4" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" t="s">
         <v>92</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="H4" t="s">
-        <v>78</v>
-      </c>
-      <c r="K4" t="s">
-        <v>93</v>
-      </c>
       <c r="N4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="23"/>
-      <c r="B5" s="79" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" s="80"/>
-      <c r="E5" s="67" t="s">
+      <c r="B5" s="62" t="s">
+        <v>55</v>
+      </c>
+      <c r="C5" s="63"/>
+      <c r="E5" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="F5" s="68"/>
-      <c r="H5" s="81" t="s">
+      <c r="F5" s="58"/>
+      <c r="H5" s="64" t="s">
         <v>1</v>
       </c>
-      <c r="I5" s="82"/>
-      <c r="K5" s="72" t="s">
+      <c r="I5" s="65"/>
+      <c r="K5" s="66" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="73"/>
-      <c r="N5" s="67" t="s">
+      <c r="L5" s="67"/>
+      <c r="N5" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="O5" s="68"/>
+      <c r="O5" s="58"/>
     </row>
     <row r="6" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="23"/>
@@ -1515,10 +1515,10 @@
       <c r="C6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E6" s="67" t="s">
+      <c r="E6" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="68"/>
+      <c r="F6" s="58"/>
       <c r="H6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1679,52 +1679,52 @@
         <v>0</v>
       </c>
       <c r="O11" s="24" t="s">
-        <v>39</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:15" ht="48.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="23"/>
-      <c r="B12" s="75" t="s">
+      <c r="B12" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="75"/>
+      <c r="C12" s="53"/>
       <c r="D12" s="25"/>
-      <c r="E12" s="75" t="s">
+      <c r="E12" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="F12" s="75"/>
+      <c r="F12" s="53"/>
       <c r="G12" s="25"/>
-      <c r="H12" s="75" t="s">
+      <c r="H12" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="I12" s="75"/>
+      <c r="I12" s="53"/>
       <c r="J12" s="25"/>
-      <c r="K12" s="75" t="s">
+      <c r="K12" s="53" t="s">
         <v>11</v>
       </c>
-      <c r="L12" s="75"/>
+      <c r="L12" s="53"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
       <c r="O12" s="26"/>
     </row>
     <row r="13" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="23"/>
-      <c r="B13" s="67" t="s">
+      <c r="B13" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="68"/>
-      <c r="E13" s="67" t="s">
+      <c r="C13" s="58"/>
+      <c r="E13" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="F13" s="68"/>
-      <c r="H13" s="67" t="s">
+      <c r="F13" s="58"/>
+      <c r="H13" s="57" t="s">
         <v>12</v>
       </c>
-      <c r="I13" s="68"/>
-      <c r="K13" s="67" t="s">
+      <c r="I13" s="58"/>
+      <c r="K13" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="L13" s="68"/>
+      <c r="L13" s="58"/>
       <c r="N13" s="15" t="s">
         <v>26</v>
       </c>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="14" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="23"/>
-      <c r="E14" s="67" t="s">
+      <c r="E14" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="F14" s="68"/>
+      <c r="F14" s="58"/>
       <c r="O14" s="24"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -1764,7 +1764,7 @@
         <v>38</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O17" s="24"/>
     </row>
@@ -1773,18 +1773,18 @@
       <c r="O18" s="24"/>
     </row>
     <row r="19" spans="1:18" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="62" t="s">
-        <v>46</v>
-      </c>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="64"/>
-      <c r="H19" s="65" t="s">
-        <v>40</v>
-      </c>
-      <c r="I19" s="66"/>
+      <c r="A19" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="61"/>
+      <c r="H19" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="I19" s="75"/>
       <c r="O19" s="24"/>
     </row>
     <row r="20" spans="1:18" ht="33" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -1815,10 +1815,10 @@
         <v>40</v>
       </c>
       <c r="O20" s="24"/>
-      <c r="Q20" s="74" t="s">
-        <v>54</v>
-      </c>
-      <c r="R20" s="74"/>
+      <c r="Q20" s="70" t="s">
+        <v>53</v>
+      </c>
+      <c r="R20" s="70"/>
     </row>
     <row r="21" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="11"/>
@@ -1846,10 +1846,10 @@
         <v>40</v>
       </c>
       <c r="O21" s="24"/>
-      <c r="Q21" s="67" t="s">
+      <c r="Q21" s="57" t="s">
         <v>0</v>
       </c>
-      <c r="R21" s="68"/>
+      <c r="R21" s="58"/>
     </row>
     <row r="22" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="11"/>
@@ -1878,10 +1878,10 @@
       </c>
       <c r="K22" s="1"/>
       <c r="O22" s="24"/>
-      <c r="Q22" s="67" t="s">
-        <v>53</v>
-      </c>
-      <c r="R22" s="68"/>
+      <c r="Q22" s="57" t="s">
+        <v>52</v>
+      </c>
+      <c r="R22" s="58"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="11"/>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="O23" s="24"/>
       <c r="Q23" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R23" s="4" t="s">
         <v>4</v>
@@ -1953,7 +1953,7 @@
       <c r="C25" s="10"/>
       <c r="D25" s="10"/>
       <c r="E25" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F25" s="6">
         <f>SUM(F20:F24)</f>
@@ -1993,7 +1993,7 @@
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
       <c r="E27" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F27" s="20">
         <f>F25/I25</f>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="O27" s="24"/>
       <c r="Q27" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R27" s="8">
         <v>0</v>
@@ -2013,31 +2013,31 @@
       <c r="O28" s="24"/>
     </row>
     <row r="29" spans="1:18" ht="20.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="62" t="s">
-        <v>45</v>
-      </c>
-      <c r="B29" s="63"/>
-      <c r="C29" s="63"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
-      <c r="F29" s="64"/>
-      <c r="H29" s="69" t="s">
-        <v>48</v>
+      <c r="A29" s="59" t="s">
+        <v>44</v>
+      </c>
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="61"/>
+      <c r="H29" s="76" t="s">
+        <v>47</v>
       </c>
       <c r="I29" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="J29" s="31" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="K29" s="31"/>
       <c r="L29" s="31"/>
       <c r="M29" s="32"/>
       <c r="O29" s="24"/>
-      <c r="Q29" s="72" t="s">
+      <c r="Q29" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="R29" s="73"/>
+      <c r="R29" s="67"/>
     </row>
     <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
@@ -2059,21 +2059,21 @@
         <f>E30*D30</f>
         <v>20</v>
       </c>
-      <c r="H30" s="70"/>
+      <c r="H30" s="77"/>
       <c r="I30" s="33" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J30" s="34" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K30" s="34"/>
       <c r="L30" s="34"/>
       <c r="M30" s="35"/>
       <c r="O30" s="24"/>
-      <c r="Q30" s="56" t="s">
+      <c r="Q30" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="R30" s="58"/>
+      <c r="R30" s="69"/>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="11"/>
@@ -2093,12 +2093,12 @@
         <f t="shared" ref="F31:F34" si="1">E31*D31</f>
         <v>40</v>
       </c>
-      <c r="H31" s="70"/>
+      <c r="H31" s="77"/>
       <c r="I31" s="33" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J31" s="34" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K31" s="34"/>
       <c r="L31" s="34"/>
@@ -2129,12 +2129,12 @@
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="H32" s="71"/>
+      <c r="H32" s="78"/>
       <c r="I32" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="J32" s="37" t="s">
         <v>59</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>60</v>
       </c>
       <c r="K32" s="37"/>
       <c r="L32" s="37"/>
@@ -2165,20 +2165,20 @@
         <f t="shared" si="1"/>
         <v>30</v>
       </c>
-      <c r="H33" s="59" t="s">
-        <v>57</v>
-      </c>
-      <c r="I33" s="60"/>
-      <c r="J33" s="60"/>
-      <c r="K33" s="60"/>
-      <c r="L33" s="60"/>
-      <c r="M33" s="61"/>
+      <c r="H33" s="71" t="s">
+        <v>56</v>
+      </c>
+      <c r="I33" s="72"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="72"/>
+      <c r="L33" s="72"/>
+      <c r="M33" s="73"/>
       <c r="O33" s="24"/>
       <c r="Q33" s="7" t="s">
         <v>38</v>
       </c>
       <c r="R33" s="14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
@@ -2205,7 +2205,7 @@
       <c r="C35" s="10"/>
       <c r="D35" s="10"/>
       <c r="E35" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F35" s="21">
         <f>SUM(F30:F34)</f>
@@ -2219,7 +2219,7 @@
       <c r="C36" s="16"/>
       <c r="D36" s="16"/>
       <c r="E36" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F36" s="20">
         <f>F35/I25</f>
@@ -2237,14 +2237,14 @@
     </row>
     <row r="37" spans="1:18" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="38" spans="1:18" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A38" s="62" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="63"/>
-      <c r="C38" s="63"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
-      <c r="F38" s="64"/>
+      <c r="A38" s="59" t="s">
+        <v>45</v>
+      </c>
+      <c r="B38" s="60"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="61"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="11">
@@ -2347,7 +2347,7 @@
       <c r="C44" s="10"/>
       <c r="D44" s="10"/>
       <c r="E44" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F44" s="6">
         <f>SUM(F39:F43)</f>
@@ -2368,7 +2368,7 @@
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
       <c r="E46" s="19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F46" s="20">
         <f>F44/I25</f>
@@ -2377,6 +2377,22 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="H33:M33"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="H29:H32"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="K13:L13"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="K12:L12"/>
@@ -2388,22 +2404,6 @@
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="N5:O5"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="H33:M33"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="H29:H32"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="61" orientation="landscape" r:id="rId1"/>
@@ -2421,71 +2421,71 @@
   <sheetData>
     <row r="4" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="H4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="L4" t="s">
-        <v>78</v>
-      </c>
-      <c r="O4" s="83" t="s">
-        <v>87</v>
-      </c>
-      <c r="P4" s="83"/>
-      <c r="Q4" s="83"/>
+        <v>77</v>
+      </c>
+      <c r="O4" s="79" t="s">
+        <v>86</v>
+      </c>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="79"/>
     </row>
     <row r="5" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="L5" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" s="83" t="s">
-        <v>88</v>
-      </c>
-      <c r="P5" s="83"/>
-      <c r="Q5" s="83"/>
+        <v>78</v>
+      </c>
+      <c r="O5" s="79" t="s">
+        <v>87</v>
+      </c>
+      <c r="P5" s="79"/>
+      <c r="Q5" s="79"/>
     </row>
     <row r="6" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="P6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
         <v>64</v>
-      </c>
-      <c r="C7" t="s">
-        <v>65</v>
       </c>
       <c r="D7">
         <v>10</v>
       </c>
       <c r="H7" t="s">
+        <v>70</v>
+      </c>
+      <c r="I7" t="s">
         <v>71</v>
       </c>
-      <c r="I7" t="s">
-        <v>72</v>
-      </c>
       <c r="L7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="O7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P7" s="39">
         <v>1</v>
@@ -2496,28 +2496,28 @@
     </row>
     <row r="8" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D8">
         <v>7</v>
       </c>
       <c r="H8" t="s">
+        <v>72</v>
+      </c>
+      <c r="I8" t="s">
         <v>73</v>
       </c>
-      <c r="I8" t="s">
-        <v>74</v>
-      </c>
       <c r="L8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="N8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="P8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="Q8">
         <v>7</v>
@@ -2525,25 +2525,25 @@
     </row>
     <row r="9" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="H9" t="s">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s">
         <v>75</v>
       </c>
-      <c r="I9" t="s">
-        <v>76</v>
-      </c>
       <c r="L9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P9" s="39">
         <v>0.75</v>
@@ -2554,16 +2554,16 @@
     </row>
     <row r="10" spans="2:17" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -2595,43 +2595,43 @@
   <sheetData>
     <row r="1" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C2" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="D2" s="57"/>
-      <c r="E2" s="58"/>
+      <c r="C2" s="68" t="s">
+        <v>111</v>
+      </c>
+      <c r="D2" s="83"/>
+      <c r="E2" s="69"/>
     </row>
     <row r="3" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C3" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="4" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C4" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C5" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="3:5" x14ac:dyDescent="0.25">
@@ -2645,43 +2645,43 @@
       <c r="E7" s="1"/>
     </row>
     <row r="8" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="56" t="s">
-        <v>95</v>
-      </c>
-      <c r="D8" s="57"/>
-      <c r="E8" s="58"/>
+      <c r="C8" s="68" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="83"/>
+      <c r="E8" s="69"/>
     </row>
     <row r="9" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C9" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C10" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C11" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D11" s="42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="3:5" x14ac:dyDescent="0.25">
@@ -2695,21 +2695,21 @@
       <c r="E13" s="1"/>
     </row>
     <row r="14" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="56" t="s">
-        <v>104</v>
-      </c>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58"/>
+      <c r="C14" s="68" t="s">
+        <v>103</v>
+      </c>
+      <c r="D14" s="83"/>
+      <c r="E14" s="69"/>
     </row>
     <row r="15" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C15" s="5">
         <v>6</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E15" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="16" spans="3:5" x14ac:dyDescent="0.25">
@@ -2717,10 +2717,10 @@
         <v>4</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2728,10 +2728,10 @@
         <v>3</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E17" s="8" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.25">
@@ -2745,121 +2745,121 @@
       <c r="E19" s="1"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="C20" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="D20" s="57"/>
-      <c r="E20" s="58"/>
+      <c r="C20" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="D20" s="83"/>
+      <c r="E20" s="69"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C21" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C22" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="C23" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="D23" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="D23" s="42" t="s">
+      <c r="E23" s="8" t="s">
         <v>109</v>
-      </c>
-      <c r="E23" s="8" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="26" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="C27" s="54"/>
-      <c r="D27" s="54"/>
-      <c r="E27" s="54"/>
-      <c r="F27" s="55"/>
-      <c r="J27" s="53" t="s">
-        <v>111</v>
-      </c>
-      <c r="K27" s="54"/>
-      <c r="L27" s="54"/>
-      <c r="M27" s="54"/>
-      <c r="N27" s="55"/>
+      <c r="B27" s="80" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="81"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="81"/>
+      <c r="F27" s="82"/>
+      <c r="J27" s="80" t="s">
+        <v>110</v>
+      </c>
+      <c r="K27" s="81"/>
+      <c r="L27" s="81"/>
+      <c r="M27" s="81"/>
+      <c r="N27" s="82"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="J28" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="K28" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="K28" s="2" t="s">
+      <c r="L28" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="L28" s="2" t="s">
+      <c r="M28" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="N28" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="M28" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="N28" s="6" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="29" spans="2:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C29" s="40" t="s">
         <v>112</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>113</v>
       </c>
       <c r="D29" s="2">
         <v>13</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F29" s="6">
         <v>1200</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="K29" s="40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M29" s="16" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N29" s="6">
         <v>3000</v>
@@ -2868,7 +2868,7 @@
     <row r="30" spans="2:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="5"/>
       <c r="C30" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D30" s="2">
         <v>9</v>
@@ -2878,16 +2878,16 @@
         <v>0</v>
       </c>
       <c r="J30" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="K30" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="L30" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="L30" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="M30" s="16" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N30" s="6">
         <v>3000</v>
@@ -2906,31 +2906,31 @@
     </row>
     <row r="32" spans="2:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B32" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="F32" s="6">
         <v>900</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K32" s="40" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="L32" s="11">
         <v>6</v>
       </c>
       <c r="M32" s="10" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N32" s="6">
         <v>3000</v>
@@ -2939,28 +2939,28 @@
     <row r="33" spans="2:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B33" s="5"/>
       <c r="C33" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="F33" s="6">
         <v>1200</v>
       </c>
       <c r="J33" s="45" t="s">
+        <v>104</v>
+      </c>
+      <c r="K33" s="46" t="s">
+        <v>127</v>
+      </c>
+      <c r="L33" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="K33" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="L33" s="47" t="s">
-        <v>106</v>
-      </c>
       <c r="M33" s="48" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N33" s="49">
         <v>3000</v>
@@ -2976,7 +2976,7 @@
       <c r="K34" s="43"/>
       <c r="L34" s="43"/>
       <c r="M34" s="51" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N34" s="52">
         <f>SUM(N29:N33)</f>
@@ -2985,22 +2985,22 @@
     </row>
     <row r="35" spans="2:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B35" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D35" s="2">
         <v>4</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F35" s="6">
         <v>1200</v>
       </c>
       <c r="J35" s="15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K35" s="43"/>
       <c r="L35" s="43"/>
@@ -3010,19 +3010,19 @@
     <row r="36" spans="2:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="5"/>
       <c r="C36" s="40" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D36" s="2">
         <v>3</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F36" s="6">
         <v>600</v>
       </c>
       <c r="J36" s="50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K36" s="43"/>
       <c r="L36" s="43"/>
@@ -3038,16 +3038,16 @@
     </row>
     <row r="38" spans="2:14" ht="45" x14ac:dyDescent="0.25">
       <c r="B38" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="C38" s="40" t="s">
+        <v>112</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C38" s="40" t="s">
-        <v>113</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="E38" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F38" s="6">
         <v>1500</v>
@@ -3056,13 +3056,13 @@
     <row r="39" spans="2:14" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B39" s="7"/>
       <c r="C39" s="41" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D39" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39" s="42" t="s">
         <v>108</v>
-      </c>
-      <c r="E39" s="42" t="s">
-        <v>109</v>
       </c>
       <c r="F39" s="8">
         <v>300</v>
@@ -3070,7 +3070,7 @@
     </row>
     <row r="41" spans="2:14" x14ac:dyDescent="0.25">
       <c r="E41" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F41">
         <f>SUM(F29:F39)</f>
